--- a/ambientes_virtuais/mysite/media/FrameWork/Planilha CIS Com IGs.xlsx
+++ b/ambientes_virtuais/mysite/media/FrameWork/Planilha CIS Com IGs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kauan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF996A-6DC3-4E72-AD5A-81B74114F6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0448B4C-81BD-452B-99DD-72843CCA7F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="675">
   <si>
     <t>CIS Sub-Control</t>
   </si>
